--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:56:02+00:00</t>
+    <t>2026-06-23T16:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:52:07+00:00</t>
+    <t>2026-06-24T09:41:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T09:41:20+00:00</t>
+    <t>2026-06-24T10:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:01:26+00:00</t>
+    <t>2026-06-24T12:42:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:42:06+00:00</t>
+    <t>2026-06-25T13:36:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:36:23+00:00</t>
+    <t>2026-06-25T13:49:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:49:59+00:00</t>
+    <t>2026-06-25T14:28:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:28:54+00:00</t>
+    <t>2026-06-30T14:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:30:17+00:00</t>
+    <t>2026-07-13T10:36:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T10:36:56+00:00</t>
+    <t>2026-07-13T14:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T14:55:38+00:00</t>
+    <t>2026-07-13T15:32:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T15:32:31+00:00</t>
+    <t>2026-07-13T15:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T15:35:13+00:00</t>
+    <t>2026-07-13T15:39:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/add-sf-ajout-doc/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T15:39:04+00:00</t>
+    <t>2026-07-15T14:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
